--- a/Design Documents/Narration/Narrative Data/Infos.xlsx
+++ b/Design Documents/Narration/Narrative Data/Infos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremias/Desktop/UNIL/MASTER/PROJET_ISH/ijo-musi/Design Documents/Narration/Narrative Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D35AC31-65AA-894B-969F-C4C7D457501C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B315A54D-212F-6D45-9D9C-5EF595681442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="28520" windowHeight="17260" activeTab="1" xr2:uid="{09E5F364-D8F4-704D-9AEF-8348B3D4D38B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="339">
   <si>
     <t>Name</t>
   </si>
@@ -1098,9 +1098,6 @@
     <t>RO: "mi lon… tenpo pini suli la, mi lon ala. taso, tenpo ni la, mi lon… mi pilin ike... lawa ona mute li utala. sina sona e ni. tenpo sina moli ala la, sina toki e ni... tenpo pini la, mi pakala e sina. taso, tenpo ni la, mi wile e ni ala... mi pakala. mi pakala suli."</t>
   </si>
   <si>
-    <t>"tomo moli li toki e ni: ''jan XXX. sina lawa e mi mute. sina sona e sewi. sina toki pona. moli sina li pilin ike tawa mi mute.''"</t>
-  </si>
-  <si>
     <t>SO: "jan XXX!", RO: "jan XXX. toki.", SO: "o toki e lon!", RO: "sina toki e seme?", *sound of searching through something, then sound of liquid in bottle*, "ni! sina sona e poki ni anu seme?!", *silence*, RO: "sina tawa insa e tomo mi? sina ken ala e ni. sina sona e ni.", SO: "tenpo ni la, ni li suli ala.", *RO cutting SO off*, RO: "ni li suli a! mi lawa. mi toki e ijo la, sina kute e ni!", SO: "pakala a! o pakala e sina! sina moli e jan XXX! sina moli e mama sewi!", RO: "o kalama ala! toki sina li ike. ni li lon ala. sina sona e ala! o pana mi e pakala poki ni!", SO: "ala a! o sina tawa mi ala!", *struggling sounds*, RO: "o pana!", SO: "ala!" *more struggling sounds, sound of bottle hitting ground then rolling*,  SO: "pakala! poki li tawa anpa...", RO: "o kute-", *RO gets cut off*, "ala! tenpo pini la, mi kepeken ilo toki e tomo moli pi mama sewi. ni la, mi kute e sina toki tawa ona. mi kute sina toki e lon. sina moli e jan XXX!", *silence*, RO: "mi-" *gets cut off*, SO: "mi tawa." *sounds of steps leaving*, RO: "ala! o awen!"</t>
   </si>
   <si>
@@ -1114,6 +1111,15 @@
   </si>
   <si>
     <t>moli, toki, e, ike, XXX</t>
+  </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
+    <t>"sounds of moving stuff*, LO: "jan pi ko li lon ni anu seme?", *RO grunting because of the physical effort* RO: "ni li lon ni.", *sounds of putting it i the chair., "LO: tenpo ni la, mi mute li pali e seme?", RO: "tenpo ni la, mi mute li awen.", *ambient sounds for a few seconds*, LO: "ni li pali ala.", RO: "ni li kama pali. o awen!", *more waiting* LO: "ni li-" *LO gets cut off, sound of magic, then sounds of SO groaning*  RO: "ni li lon! jan sewi wan li lon!", LO: "pona a!", *more groaning*, LO: "ni li toke e seme?", RO: "ni li toki ala. tenpo ni la, ni li sona ala e toki." *some more groaning*, RO: "mi mute li-", *gets cut off by groan*, RO (angrily): "o kalama ala! mi mute li pana sona e toki pona.", *silence*, LO: "mi ken ala ken e ni: nimi e ona?", RO: "sina ken ala e ni. tenpo pini la, mi nimi e ona.", LO (disappointed): "nimi ona li seme?", RO: *says SO's name.</t>
+  </si>
+  <si>
+    <t>*sounds of putting EO against tree, LO crying*, RO: "lon.", *EO coughs", EO: "pali sina mute li pona tawa mi.", LO (crying): "ni li ala a! pali mi li moli e sina. pakala e mi!" *EO coughs some more*, EO (gently): "o kamala ala! sina pona. tenpo moli mi la, mi moli. pali sina li moli ala e mi.", LO: "taso, tenpo pini la, mi pali e moku. tenpo pini la, sina moku e ni. tenpo ni la, sina moli tan moku ni.", EO: "mi moli, tan moli mi li lon. moku sina li suli ala.", LO: "taso-", *cut off by EO*, EO: "moli mi li lon, LO. moli mi li lon la, ni li sewi. sina sona e ni: ale li sewi.", LO: "taso mi pilin ike. mi pilin ike suli a!", EO: "pilin sina li lon. pilin sina li sewi. pilin sina li pona. ale li pona. sina sona e ni anu seme?", LO (sniffing): "mi li sona e ni.", EO: "pona a!" *coughing*, "jan LO. o tawa! tenpo ni la, mi wile toki tawa jan SO.", LO: "mi tawa." *sounds of steps, then silence*, EO: "sina wile toki tawa mi e ijo?", RO: "sina toki e seme?", EO: "mi sona e lon", RO: "lon seme?", *sigh*, EO: "mi sona e lon ni: sina pana insa moku e telo moli.", *silence*, RO: "mi-", *gets cut off*, EO: "ni li ike. ni li pakala a! taso ni li lon. tenpo kama lili la, mi moli., RO: "taso-", EO: "o kamala ala! o sina kute e mi! tenpo kama la, sina toki tawa jan LO e lon. sina sona e ni?", RO: "taso-" *gets cut off*, EO(sharply): "sina. sona. e. ni?" *small silence*, RO: "mi sona e ni.", EO: "pona a!"</t>
   </si>
 </sst>
 </file>
@@ -3927,7 +3933,7 @@
         <v>315</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
@@ -3944,13 +3950,13 @@
         <v>284</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>334</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
@@ -4029,6 +4035,9 @@
       <c r="D7" s="6" t="s">
         <v>294</v>
       </c>
+      <c r="H7" s="6" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
@@ -4046,7 +4055,9 @@
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="H8" s="9" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
@@ -4062,10 +4073,10 @@
         <v>293</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>330</v>

--- a/Design Documents/Narration/Narrative Data/Infos.xlsx
+++ b/Design Documents/Narration/Narrative Data/Infos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremias/Desktop/UNIL/MASTER/PROJET_ISH/ijo-musi/Design Documents/Narration/Narrative Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B315A54D-212F-6D45-9D9C-5EF595681442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD697228-2E74-BB41-B231-6D94A444F34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="28520" windowHeight="17260" activeTab="1" xr2:uid="{09E5F364-D8F4-704D-9AEF-8348B3D4D38B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="340">
   <si>
     <t>Name</t>
   </si>
@@ -1120,13 +1120,16 @@
   </si>
   <si>
     <t>*sounds of putting EO against tree, LO crying*, RO: "lon.", *EO coughs", EO: "pali sina mute li pona tawa mi.", LO (crying): "ni li ala a! pali mi li moli e sina. pakala e mi!" *EO coughs some more*, EO (gently): "o kamala ala! sina pona. tenpo moli mi la, mi moli. pali sina li moli ala e mi.", LO: "taso, tenpo pini la, mi pali e moku. tenpo pini la, sina moku e ni. tenpo ni la, sina moli tan moku ni.", EO: "mi moli, tan moli mi li lon. moku sina li suli ala.", LO: "taso-", *cut off by EO*, EO: "moli mi li lon, LO. moli mi li lon la, ni li sewi. sina sona e ni: ale li sewi.", LO: "taso mi pilin ike. mi pilin ike suli a!", EO: "pilin sina li lon. pilin sina li sewi. pilin sina li pona. ale li pona. sina sona e ni anu seme?", LO (sniffing): "mi li sona e ni.", EO: "pona a!" *coughing*, "jan LO. o tawa! tenpo ni la, mi wile toki tawa jan SO.", LO: "mi tawa." *sounds of steps, then silence*, EO: "sina wile toki tawa mi e ijo?", RO: "sina toki e seme?", EO: "mi sona e lon", RO: "lon seme?", *sigh*, EO: "mi sona e lon ni: sina pana insa moku e telo moli.", *silence*, RO: "mi-", *gets cut off*, EO: "ni li ike. ni li pakala a! taso ni li lon. tenpo kama lili la, mi moli., RO: "taso-", EO: "o kamala ala! o sina kute e mi! tenpo kama la, sina toki tawa jan LO e lon. sina sona e ni?", RO: "taso-" *gets cut off*, EO(sharply): "sina. sona. e. ni?" *small silence*, RO: "mi sona e ni.", EO: "pona a!"</t>
+  </si>
+  <si>
+    <t>ANNULER CRAFT ROOM, DÉPLACER SCÈNES VER AUTRES SALLES</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1146,8 +1149,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri (Body)"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1166,6 +1175,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1179,7 +1194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1211,11 +1226,17 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="29">
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1549,44 +1570,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A333011E-814B-4044-8CEE-912E2F961A31}" name="Table1" displayName="Table1" ref="A1:J78" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A333011E-814B-4044-8CEE-912E2F961A31}" name="Table1" displayName="Table1" ref="A1:J78" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="A1:J78" xr:uid="{A333011E-814B-4044-8CEE-912E2F961A31}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J78">
     <sortCondition ref="B1:B78"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A3972590-6843-E64D-BC8B-BE7F61021465}" name="Name" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{C3FDF78C-9C8A-384C-A991-91CE1FE2E698}" name="Mystery" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{B29A1B80-6D4C-4B4E-8DDE-8665F64956DF}" name="Info" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{8A8BB49C-F3B9-124C-AAA9-B71B4638E352}" name="Room" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{FB141D1B-4AA2-5546-ABCB-9120591D12F1}" name="Medium" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{D8B5D0BC-C917-6243-9E21-EFCAC6482479}" name="Timing / 5" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{0B157806-E1A4-6043-AA30-D1E15F12C568}" name="Findable" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{51D56085-B0C3-E841-B846-C22EDBD243D9}" name="Understandable" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{29BFBE76-ABF1-5E49-B5EE-417D1C8C1B44}" name="Difficulty" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{A3972590-6843-E64D-BC8B-BE7F61021465}" name="Name" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{C3FDF78C-9C8A-384C-A991-91CE1FE2E698}" name="Mystery" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{B29A1B80-6D4C-4B4E-8DDE-8665F64956DF}" name="Info" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{8A8BB49C-F3B9-124C-AAA9-B71B4638E352}" name="Room" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{FB141D1B-4AA2-5546-ABCB-9120591D12F1}" name="Medium" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{D8B5D0BC-C917-6243-9E21-EFCAC6482479}" name="Timing / 5" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{0B157806-E1A4-6043-AA30-D1E15F12C568}" name="Findable" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{51D56085-B0C3-E841-B846-C22EDBD243D9}" name="Understandable" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{29BFBE76-ABF1-5E49-B5EE-417D1C8C1B44}" name="Difficulty" dataDxfId="12">
       <calculatedColumnFormula xml:space="preserve"> SQRT((Table1[[#This Row],[Understandable]]^2) + (Table1[[#This Row],[Findable]]^2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{44F0299F-D12F-334D-95A5-FD753E4B8195}" name="Ideas and notes" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{44F0299F-D12F-334D-95A5-FD753E4B8195}" name="Ideas and notes" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A8B0A543-28F6-294F-8B07-E17D8AA06C2B}" name="Table3" displayName="Table3" ref="A1:H14" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H14" xr:uid="{A8B0A543-28F6-294F-8B07-E17D8AA06C2B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A8B0A543-28F6-294F-8B07-E17D8AA06C2B}" name="Table3" displayName="Table3" ref="A1:I14" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I14" xr:uid="{A8B0A543-28F6-294F-8B07-E17D8AA06C2B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H14">
     <sortCondition ref="C1:C14"/>
   </sortState>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{1355E863-F6E3-D349-91CC-66026BF92E65}" name="id" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{11B5C82D-9182-164A-AC1A-C7860136E82F}" name="infos" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{A4DAD171-1D30-194C-B63A-3BC9D929AA6C}" name="place" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{FD04A320-3781-4743-BBB2-47BBED4853F8}" name="object" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{6A83D1B3-B3D1-824B-A40A-3434A2205F56}" name="sentence" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{A3C2C38B-7967-F649-A4A6-C189FCD5B493}" name="hidden_words" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{5217A8AB-14D0-7B41-B779-58D056DC5244}" name="clues" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{929F8BC9-DAB2-A945-B46C-9F9644C93C91}" name="dialog" dataDxfId="0"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{1355E863-F6E3-D349-91CC-66026BF92E65}" name="id" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{11B5C82D-9182-164A-AC1A-C7860136E82F}" name="infos" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{A4DAD171-1D30-194C-B63A-3BC9D929AA6C}" name="place" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{FD04A320-3781-4743-BBB2-47BBED4853F8}" name="object" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{6A83D1B3-B3D1-824B-A40A-3434A2205F56}" name="sentence" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{A3C2C38B-7967-F649-A4A6-C189FCD5B493}" name="hidden_words" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{5217A8AB-14D0-7B41-B779-58D056DC5244}" name="clues" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{929F8BC9-DAB2-A945-B46C-9F9644C93C91}" name="dialog" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{4504C8B3-C3D5-0642-82F0-A45484DBCC8E}" name="ANNULER CRAFT ROOM, DÉPLACER SCÈNES VER AUTRES SALLES" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2583,7 +2605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="108" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="126" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>88</v>
       </c>
@@ -3030,7 +3052,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>76</v>
       </c>
@@ -3375,7 +3397,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>60</v>
       </c>
@@ -3732,7 +3754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="54" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" ht="72" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>62</v>
       </c>
@@ -3849,22 +3871,22 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="containsText" dxfId="27" priority="1" operator="containsText" text="East">
+    <cfRule type="containsText" dxfId="28" priority="1" operator="containsText" text="East">
       <formula>NOT(ISERROR(SEARCH("East",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="2" operator="containsText" text="Waiting">
+    <cfRule type="containsText" dxfId="27" priority="2" operator="containsText" text="Waiting">
       <formula>NOT(ISERROR(SEARCH("Waiting",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="3" operator="containsText" text="Sacred">
+    <cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="Sacred">
       <formula>NOT(ISERROR(SEARCH("Sacred",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="4" operator="containsText" text="Pond">
+    <cfRule type="containsText" dxfId="25" priority="4" operator="containsText" text="Pond">
       <formula>NOT(ISERROR(SEARCH("Pond",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="5" operator="containsText" text="Balcony">
+    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="Balcony">
       <formula>NOT(ISERROR(SEARCH("Balcony",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="6" operator="containsText" text="Craft">
+    <cfRule type="containsText" dxfId="23" priority="6" operator="containsText" text="Craft">
       <formula>NOT(ISERROR(SEARCH("Craft",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3877,17 +3899,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70BDF2BC-5ADE-0B4A-AAFC-D255F3A83AC7}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="40.83203125" defaultRowHeight="120" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="40.83203125" style="6"/>
     <col min="3" max="3" width="16.5" style="6" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" style="6" customWidth="1"/>
     <col min="5" max="5" width="43.83203125" style="6" customWidth="1"/>
-    <col min="6" max="16384" width="40.83203125" style="6"/>
+    <col min="6" max="8" width="40.83203125" style="6"/>
+    <col min="9" max="9" width="107.5" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="40.83203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="5" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>260</v>
       </c>
@@ -3912,8 +3936,11 @@
       <c r="H1" s="5" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I1" s="11" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>267</v>
       </c>
@@ -3936,7 +3963,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>268</v>
       </c>
@@ -3959,7 +3986,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>269</v>
       </c>
@@ -3982,7 +4009,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>271</v>
       </c>
@@ -3999,7 +4026,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>272</v>
       </c>
@@ -4022,7 +4049,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>274</v>
       </c>
@@ -4039,7 +4066,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>275</v>
       </c>
@@ -4059,7 +4086,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>273</v>
       </c>
@@ -4082,7 +4109,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="9" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" s="9" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>276</v>
       </c>
@@ -4100,7 +4127,7 @@
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>270</v>
       </c>
@@ -4123,7 +4150,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>277</v>
       </c>
@@ -4137,7 +4164,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>311</v>
       </c>
@@ -4151,7 +4178,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>278</v>
       </c>
